--- a/agriculture 13.xlsx
+++ b/agriculture 13.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
-  <si>
-    <t xml:space="preserve">Annual Growth Rate - Rice</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
   <si>
     <t xml:space="preserve">APY Statistics of Rice in India (1950-22)</t>
   </si>
@@ -310,11 +307,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#.##"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -330,14 +328,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -419,24 +409,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -444,7 +430,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -456,7 +442,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -464,7 +450,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -485,1118 +471,1108 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S80"/>
-  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S1048576"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.04"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="6" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="6" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="7" t="n">
+        <v>-3.18078545926648</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3.49854227405249</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>6.9001137792682</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>-3.18078545926648</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>3.49854227405249</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>6.9001137792682</v>
+      <c r="B6" s="7" t="n">
+        <v>0.469326181696284</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>7.51173708920188</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>7.00931307331421</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>0.469326181696284</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>7.51173708920188</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>7.00931307331421</v>
+      <c r="B7" s="7" t="n">
+        <v>4.40440440440442</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>23.1877729257642</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>17.9911006412773</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>4.40440440440442</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>23.1877729257642</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>17.9911006412773</v>
+      <c r="B8" s="7" t="n">
+        <v>-1.6618728028124</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>-10.5990783410138</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>-9.0885899042781</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>-1.6618728028124</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>-10.5990783410138</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>-9.0885899042781</v>
+      <c r="B9" s="7" t="n">
+        <v>2.43743906402341</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>9.27835051546391</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>6.67862328123665</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>2.43743906402341</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>9.27835051546391</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>6.67862328123665</v>
+      <c r="B10" s="7" t="n">
+        <v>2.41116751269037</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>5.3701015965167</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2.88893717762504</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>2.41116751269037</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>5.3701015965167</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>2.88893717762504</v>
+      <c r="B11" s="7" t="n">
+        <v>0.0619578686493094</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>-12.0867768595041</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>-12.1416582372753</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0.0619578686493094</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>-12.0867768595041</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>-12.1416582372753</v>
+      <c r="B12" s="7" t="n">
+        <v>2.69349845201239</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>20.8382295338817</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>17.6695344129555</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>2.69349845201239</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>20.8382295338817</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>17.6695344129555</v>
+      <c r="B13" s="7" t="n">
+        <v>1.95960205004522</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>2.69043760129659</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.716082833365594</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>1.95960205004522</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>2.69043760129659</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>0.716082833365594</v>
+      <c r="B14" s="7" t="n">
+        <v>0.916617386162044</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>9.1540404040404</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>8.16252455376205</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>0.916617386162044</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>9.1540404040404</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>8.16252455376205</v>
+      <c r="B15" s="7" t="n">
+        <v>1.6407852329329</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>3.12319259687681</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1.45877336702265</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>1.6407852329329</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>3.12319259687681</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>1.45877336702265</v>
+      <c r="B16" s="7" t="n">
+        <v>2.8826751225137</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>-6.87044307347167</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>-9.47994085372972</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="8" t="n">
-        <v>2.8826751225137</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>-6.87044307347167</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>-9.47994085372972</v>
+      <c r="B17" s="7" t="n">
+        <v>0.336228635472136</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>11.4122252333634</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>11.0391075861624</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="8" t="n">
-        <v>0.336228635472136</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>11.4122252333634</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>11.0391075861624</v>
+      <c r="B18" s="7" t="n">
+        <v>1.81513543702876</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>6.24324324324326</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>4.349467204785</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="8" t="n">
-        <v>1.81513543702876</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>6.24324324324326</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>4.349467204785</v>
+      <c r="B19" s="7" t="n">
+        <v>-2.71530444322545</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>-22.1826507250064</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>-20.0107589712198</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>-2.71530444322545</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>-22.1826507250064</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>-20.0107589712198</v>
+      <c r="B20" s="7" t="n">
+        <v>-0.620242458415554</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>-0.490356325596597</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.0672526147352803</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="8" t="n">
-        <v>-0.620242458415554</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>-0.490356325596597</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>0.0672526147352803</v>
+      <c r="B21" s="7" t="n">
+        <v>3.37588652482268</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>23.5545335085414</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>19.595596755504</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>3.37588652482268</v>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>23.5545335085414</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>19.595596755504</v>
+      <c r="B22" s="7" t="n">
+        <v>1.45444566410538</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>5.71656474341931</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>4.25245371132923</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>1.45444566410538</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>5.71656474341931</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>4.25245371132923</v>
+      <c r="B23" s="7" t="n">
+        <v>1.92047606167163</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>1.68511066398391</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>-0.280669144981416</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="8" t="n">
-        <v>1.92047606167163</v>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>1.68511066398391</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>-0.280669144981416</v>
+      <c r="B24" s="7" t="n">
+        <v>-0.238853503184699</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>4.42740539203561</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>4.67762679639883</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>-0.238853503184699</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>4.42740539203561</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>4.67762679639883</v>
+      <c r="B25" s="7" t="n">
+        <v>0.452247938281447</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>2.01326385599243</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1.55452870001871</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="8" t="n">
-        <v>0.452247938281447</v>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>2.01326385599243</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>1.55452870001871</v>
+      <c r="B26" s="7" t="n">
+        <v>-2.83368644067796</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>-8.89250058045042</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>-6.23602745850979</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="8" t="n">
-        <v>-2.83368644067796</v>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>-8.89250058045042</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>-6.23602745850979</v>
+      <c r="B27" s="7" t="n">
+        <v>4.36086127010085</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>12.2579001019368</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>7.62038335670874</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="8" t="n">
-        <v>4.36086127010085</v>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>12.2579001019368</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>7.62038335670874</v>
+      <c r="B28" s="7" t="n">
+        <v>-1.04465917994254</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>-10.1475595913734</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>-9.24413553431799</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="8" t="n">
-        <v>-1.04465917994254</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>-10.1475595913734</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>-9.24413553431799</v>
+      <c r="B29" s="7" t="n">
+        <v>4.19635787806809</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>23.1430015159171</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>18.1839938732529</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="8" t="n">
-        <v>4.19635787806809</v>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>23.1430015159171</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>18.1839938732529</v>
+      <c r="B30" s="7" t="n">
+        <v>-2.45694022289766</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>-13.9926138695117</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>-11.8261714794865</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="8" t="n">
-        <v>-2.45694022289766</v>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>-13.9926138695117</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>-11.8261714794865</v>
+      <c r="B31" s="7" t="n">
+        <v>4.59620877694107</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>25.6440839694656</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>20.1230995360801</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="8" t="n">
-        <v>4.59620877694107</v>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>25.6440839694656</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>20.1230995360801</v>
+      <c r="B32" s="7" t="n">
+        <v>0.496524329692138</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>2.08847541294854</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>1.58381768124809</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="8" t="n">
-        <v>0.496524329692138</v>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>2.08847541294854</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>1.58381768124809</v>
+      <c r="B33" s="7" t="n">
+        <v>-2.6185770750988</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>-21.2758043518691</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>-19.1589312735732</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="8" t="n">
-        <v>-2.6185770750988</v>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>-21.2758043518691</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>-19.1589312735732</v>
+      <c r="B34" s="7" t="n">
+        <v>1.85185185185184</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>26.6950153555398</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>24.3914250060532</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="8" t="n">
-        <v>1.85185185185184</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>26.6950153555398</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>24.3914250060532</v>
+      <c r="B35" s="7" t="n">
+        <v>1.39476961394771</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>-0.708558642550816</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>-2.07450551754084</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="8" t="n">
-        <v>1.39476961394771</v>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>-0.708558642550816</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>-2.07450551754084</v>
+      <c r="B36" s="7" t="n">
+        <v>-6.01817735200197</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>-11.5117370892019</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>-5.88900866188085</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="8" t="n">
-        <v>-6.01817735200197</v>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>-11.5117370892019</v>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>-5.88900866188085</v>
+      <c r="B37" s="7" t="n">
+        <v>7.78881338212234</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>27.5466893039049</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>18.3850528025995</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="8" t="n">
-        <v>7.78881338212234</v>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>27.5466893039049</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>18.3850528025995</v>
+      <c r="B38" s="7" t="n">
+        <v>-0.193986420950543</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>-2.92845257903493</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>-2.73927483325556</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="8" t="n">
-        <v>-0.193986420950543</v>
-      </c>
-      <c r="C39" s="8" t="n">
-        <v>-2.92845257903493</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>-2.73927483325556</v>
+      <c r="B39" s="7" t="n">
+        <v>-0.0485908649173861</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>9.41035310250255</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>9.46310145336531</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="8" t="n">
-        <v>-0.0485908649173861</v>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>9.41035310250255</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>9.46310145336531</v>
+      <c r="B40" s="7" t="n">
+        <v>0.0729217306757457</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>-5.12298292339025</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>-5.19229405812327</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="8" t="n">
-        <v>0.0729217306757457</v>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>-5.12298292339025</v>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>-5.19229405812327</v>
+      <c r="B41" s="7" t="n">
+        <v>-5.73232936604323</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>-6.10964332892999</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>-0.3997362284751</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="8" t="n">
-        <v>-5.73232936604323</v>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>-6.10964332892999</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>-0.3997362284751</v>
+      <c r="B42" s="7" t="n">
+        <v>7.5238340633857</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>23.97115722828</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>15.295988642336</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="8" t="n">
-        <v>7.5238340633857</v>
-      </c>
-      <c r="C43" s="8" t="n">
-        <v>23.97115722828</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>15.295988642336</v>
+      <c r="B43" s="7" t="n">
+        <v>1.05439731607957</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>4.36941410129097</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>3.28086242518604</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="8" t="n">
-        <v>1.05439731607957</v>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>4.36941410129097</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>3.28086242518604</v>
+      <c r="B44" s="7" t="n">
+        <v>1.23310410244248</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>0.978659779801561</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>-0.251632169940552</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="8" t="n">
-        <v>1.23310410244248</v>
-      </c>
-      <c r="C45" s="8" t="n">
-        <v>0.978659779801561</v>
-      </c>
-      <c r="D45" s="8" t="n">
-        <v>-0.251632169940552</v>
+      <c r="B45" s="7" t="n">
+        <v>-0.093698758491445</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>0.524969713285772</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0.619461907115193</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="8" t="n">
-        <v>-0.093698758491445</v>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>0.524969713285772</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>0.619461907115193</v>
+      <c r="B46" s="7" t="n">
+        <v>-2.03985932004689</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>-2.43706480985539</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>-0.405482581382066</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="8" t="n">
-        <v>-2.03985932004689</v>
-      </c>
-      <c r="C47" s="8" t="n">
-        <v>-2.43706480985539</v>
-      </c>
-      <c r="D47" s="8" t="n">
-        <v>-0.405482581382066</v>
+      <c r="B47" s="7" t="n">
+        <v>1.81905217807563</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>10.2113642602251</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>8.24244509432881</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="8" t="n">
-        <v>1.81905217807563</v>
-      </c>
-      <c r="C48" s="8" t="n">
-        <v>10.2113642602251</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>8.24244509432881</v>
+      <c r="B48" s="7" t="n">
+        <v>0.634696755994368</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1.8804483188045</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>1.23752410417239</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="8" t="n">
-        <v>0.634696755994368</v>
-      </c>
-      <c r="C49" s="8" t="n">
-        <v>1.8804483188045</v>
-      </c>
-      <c r="D49" s="8" t="n">
-        <v>1.23752410417239</v>
+      <c r="B49" s="7" t="n">
+        <v>0.0700770847932741</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>-5.90392372570591</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>-5.96964939822082</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="8" t="n">
-        <v>0.0700770847932741</v>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>-5.90392372570591</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>-5.96964939822082</v>
+      <c r="B50" s="7" t="n">
+        <v>1.37721755368814</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>6.18342426604313</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>3.44812234267524</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B51" s="8" t="n">
-        <v>1.37721755368814</v>
-      </c>
-      <c r="C51" s="8" t="n">
-        <v>6.18342426604313</v>
-      </c>
-      <c r="D51" s="8" t="n">
-        <v>3.44812234267524</v>
+      <c r="B51" s="7" t="n">
+        <v>0.0460511167395872</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>0.966479080009797</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>2.21208469616112</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B52" s="8" t="n">
-        <v>0.0460511167395872</v>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>0.966479080009797</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>2.21208469616112</v>
+      <c r="B52" s="7" t="n">
+        <v>3.10701956271575</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>4.3014661335272</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>1.12789473684212</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="8" t="n">
-        <v>3.10701956271575</v>
-      </c>
-      <c r="C53" s="8" t="n">
-        <v>4.3014661335272</v>
-      </c>
-      <c r="D53" s="8" t="n">
-        <v>1.12789473684212</v>
+      <c r="B53" s="7" t="n">
+        <v>0.803571428571437</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>4.182156133829</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>3.36051794757028</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="8" t="n">
-        <v>0.803571428571437</v>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>4.182156133829</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>3.36051794757028</v>
+      <c r="B54" s="7" t="n">
+        <v>-0.99645704162975</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>-5.24085637823373</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>-4.29556898288016</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="8" t="n">
-        <v>-0.99645704162975</v>
-      </c>
-      <c r="C55" s="8" t="n">
-        <v>-5.24085637823373</v>
-      </c>
-      <c r="D55" s="8" t="n">
-        <v>-4.29556898288016</v>
+      <c r="B55" s="7" t="n">
+        <v>0.424960858868251</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>9.83760884914098</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>9.38132993807512</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="8" t="n">
-        <v>0.424960858868251</v>
-      </c>
-      <c r="C56" s="8" t="n">
-        <v>9.83760884914098</v>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>9.38132993807512</v>
+      <c r="B56" s="7" t="n">
+        <v>-8.28507795100223</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>-23.0554960359974</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>-16.1135161135161</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B57" s="8" t="n">
-        <v>-8.28507795100223</v>
-      </c>
-      <c r="C57" s="8" t="n">
-        <v>-23.0554960359974</v>
-      </c>
-      <c r="D57" s="8" t="n">
-        <v>-16.1135161135161</v>
+      <c r="B57" s="7" t="n">
+        <v>3.4239922292375</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>23.2664995822891</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>19.1714449541284</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="8" t="n">
-        <v>3.4239922292375</v>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>23.2664995822891</v>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>19.1714449541284</v>
+      <c r="B58" s="7" t="n">
+        <v>-1.59661892463021</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>-6.0996272450017</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>-4.53965886400269</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="8" t="n">
-        <v>-1.59661892463021</v>
-      </c>
-      <c r="C59" s="8" t="n">
-        <v>-6.0996272450017</v>
-      </c>
-      <c r="D59" s="8" t="n">
-        <v>-4.53965886400269</v>
+      <c r="B59" s="7" t="n">
+        <v>4.17561441183489</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>10.4174185011428</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>5.9475806451613</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B60" s="8" t="n">
-        <v>4.17561441183489</v>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>10.4174185011428</v>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>5.9475806451613</v>
+      <c r="B60" s="7" t="n">
+        <v>0.343563902885946</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>1.71042597232813</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>1.36726926736441</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="8" t="n">
-        <v>0.343563902885946</v>
-      </c>
-      <c r="C61" s="8" t="n">
-        <v>1.71042597232813</v>
-      </c>
-      <c r="D61" s="8" t="n">
-        <v>1.36726926736441</v>
+      <c r="B61" s="7" t="n">
+        <v>0.228258388495761</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>3.56683804627249</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>3.33733820175151</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B62" s="8" t="n">
-        <v>0.228258388495761</v>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>3.56683804627249</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>3.33733820175151</v>
+      <c r="B62" s="7" t="n">
+        <v>3.71213846504215</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>2.57524045919952</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>-1.08136339895997</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B63" s="8" t="n">
-        <v>3.71213846504215</v>
-      </c>
-      <c r="C63" s="8" t="n">
-        <v>2.57524045919952</v>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>-1.08136339895997</v>
+      <c r="B63" s="7" t="n">
+        <v>-7.94905577514272</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>-10.1734220608994</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>-2.41731097684157</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B64" s="8" t="n">
-        <v>-7.94905577514272</v>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>-10.1734220608994</v>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>-2.41731097684157</v>
+      <c r="B64" s="7" t="n">
+        <v>2.24236641221374</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>7.73375238522842</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>5.35760495720787</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B65" s="8" t="n">
-        <v>2.24236641221374</v>
-      </c>
-      <c r="C65" s="8" t="n">
-        <v>7.73375238522842</v>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>5.35760495720787</v>
+      <c r="B65" s="7" t="n">
+        <v>2.68315445636957</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>9.71035632423421</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>6.8585157596706</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B66" s="8" t="n">
-        <v>2.68315445636957</v>
-      </c>
-      <c r="C66" s="8" t="n">
-        <v>9.71035632423421</v>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>6.8585157596706</v>
+      <c r="B66" s="7" t="n">
+        <v>-2.86298568507157</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>-0.0664767331433946</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>2.8627070761104</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="8" t="n">
-        <v>-2.86298568507157</v>
-      </c>
-      <c r="C67" s="8" t="n">
-        <v>-0.0664767331433946</v>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>2.8627070761104</v>
+      <c r="B67" s="7" t="n">
+        <v>3.25146198830411</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>1.3494250688967</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>-1.8298975354888</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="8" t="n">
-        <v>3.25146198830411</v>
-      </c>
-      <c r="C68" s="8" t="n">
-        <v>1.3494250688967</v>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>-1.8298975354888</v>
+      <c r="B68" s="7" t="n">
+        <v>-0.0679655641141808</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>-1.09704641350211</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>-1.0342258825477</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="8" t="n">
-        <v>-0.0679655641141808</v>
-      </c>
-      <c r="C69" s="8" t="n">
-        <v>-1.09704641350211</v>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>-1.0342258825477</v>
+      <c r="B69" s="7" t="n">
+        <v>-1.38290637043754</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>-1.01441031475162</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>0.373017300140921</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="8" t="n">
-        <v>-1.38290637043754</v>
-      </c>
-      <c r="C70" s="8" t="n">
-        <v>-1.01441031475162</v>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>0.373017300140921</v>
+      <c r="B70" s="7" t="n">
+        <v>1.1264367816092</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>5.0665645053156</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>3.88671085687622</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B71" s="8" t="n">
-        <v>1.1264367816092</v>
-      </c>
-      <c r="C71" s="8" t="n">
-        <v>5.0665645053156</v>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>3.88671085687622</v>
+      <c r="B71" s="7" t="n">
+        <v>-0.500113662195956</v>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>2.7894257064722</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>3.30376335461517</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B72" s="8" t="n">
-        <v>-0.500113662195956</v>
-      </c>
-      <c r="C72" s="8" t="n">
-        <v>2.7894257064722</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>3.30376335461517</v>
+      <c r="B72" s="7" t="n">
+        <v>0.891021247429724</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>3.29904221355091</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>2.40459645172562</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B73" s="8" t="n">
-        <v>0.891021247429724</v>
-      </c>
-      <c r="C73" s="8" t="n">
-        <v>3.29904221355091</v>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>2.40459645172562</v>
+      <c r="B73" s="7" t="n">
+        <v>-1.1322463768116</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>2.0518543956044</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>3.20906499256965</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B74" s="8" t="n">
-        <v>-1.1322463768116</v>
-      </c>
-      <c r="C74" s="8" t="n">
-        <v>2.0518543956044</v>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>3.20906499256965</v>
-      </c>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7" t="n">
+        <v>4.62690333978295</v>
+      </c>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8" t="n">
-        <v>4.62690333978295</v>
-      </c>
-      <c r="D75" s="8"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7" t="n">
+        <v>4.25343732411352</v>
+      </c>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7" t="n">
+        <v>-4.07990128027147</v>
+      </c>
+      <c r="D76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7" t="n">
+        <v>4.25343732411352</v>
+      </c>
+      <c r="D77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8" t="n">
-        <v>4.25343732411352</v>
-      </c>
-      <c r="D76" s="8"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8" t="n">
-        <v>-4.07990128027147</v>
-      </c>
-      <c r="D77" s="8"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="s">
-        <v>77</v>
-      </c>
       <c r="B78" s="8"/>
-      <c r="C78" s="8" t="n">
-        <v>4.25343732411352</v>
-      </c>
+      <c r="C78" s="8"/>
       <c r="D78" s="8"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="9" t="s">
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+      <c r="N78" s="8"/>
+      <c r="O78" s="8"/>
+      <c r="P78" s="8"/>
+      <c r="Q78" s="8"/>
+      <c r="R78" s="8"/>
+      <c r="S78" s="9"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9"/>
-      <c r="L79" s="9"/>
-      <c r="M79" s="9"/>
-      <c r="N79" s="9"/>
-      <c r="O79" s="9"/>
-      <c r="P79" s="9"/>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="10"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
+      <c r="K79" s="10"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="10"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
       <c r="S79" s="10"/>
     </row>
-    <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="11"/>
-      <c r="O80" s="11"/>
-      <c r="P80" s="11"/>
-      <c r="Q80" s="11"/>
-      <c r="R80" s="11"/>
-      <c r="S80" s="11"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A79:R79"/>
-    <mergeCell ref="A80:S80"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A78:R78"/>
+    <mergeCell ref="A79:S79"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 13.xlsx
+++ b/agriculture 13.xlsx
@@ -20,18 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
   <si>
-    <t xml:space="preserve">Area (Million Hectares)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production (Million Tonnes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yield Kg./Hectare</t>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield </t>
   </si>
   <si>
     <t xml:space="preserve">1950-51</t>
@@ -248,6 +248,26 @@
   </si>
   <si>
     <t xml:space="preserve">2021-22</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Unit:- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Area - Million Hectares, Production - Million Tonnes, Yield - Kg./Hectare</t>
+    </r>
   </si>
   <si>
     <r>
@@ -257,7 +277,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source: </t>
     </r>
@@ -267,7 +286,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">EPWRF (Economic &amp; Political Weekly Research Foundation) 1950-2021</t>
     </r>
@@ -280,7 +298,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Description : </t>
     </r>
@@ -290,7 +307,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -304,7 +320,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#.##"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -332,14 +348,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -391,7 +419,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -400,27 +428,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -429,6 +465,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -450,1100 +490,1101 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S1048576"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.04"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>-3.18078545926648</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>3.49854227405249</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>6.9001137792682</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
+      <c r="A4" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>-3.18078545926648</v>
+        <v>0.469326181696284</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3.49854227405249</v>
+        <v>7.51173708920188</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.9001137792682</v>
+        <v>7.00931307331421</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
+      <c r="A5" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.469326181696284</v>
+        <v>4.40440440440442</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7.51173708920188</v>
+        <v>23.1877729257642</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7.00931307331421</v>
+        <v>17.9911006412773</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>7</v>
+      <c r="A6" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>4.40440440440442</v>
+        <v>-1.6618728028124</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>23.1877729257642</v>
+        <v>-10.5990783410138</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>17.9911006412773</v>
+        <v>-9.0885899042781</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
+      <c r="A7" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>-1.6618728028124</v>
+        <v>2.43743906402341</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-10.5990783410138</v>
+        <v>9.27835051546391</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-9.0885899042781</v>
+        <v>6.67862328123665</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
+      <c r="A8" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2.43743906402341</v>
+        <v>2.41116751269037</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>9.27835051546391</v>
+        <v>5.3701015965167</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>6.67862328123665</v>
+        <v>2.88893717762504</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
+      <c r="A9" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2.41116751269037</v>
+        <v>0.0619578686493094</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5.3701015965167</v>
+        <v>-12.0867768595041</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2.88893717762504</v>
+        <v>-12.1416582372753</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
+      <c r="A10" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.0619578686493094</v>
+        <v>2.69349845201239</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>-12.0867768595041</v>
+        <v>20.8382295338817</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>-12.1416582372753</v>
+        <v>17.6695344129555</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>12</v>
+      <c r="A11" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2.69349845201239</v>
+        <v>1.95960205004522</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>20.8382295338817</v>
+        <v>2.69043760129659</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>17.6695344129555</v>
+        <v>0.716082833365594</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>13</v>
+      <c r="A12" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1.95960205004522</v>
+        <v>0.916617386162044</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2.69043760129659</v>
+        <v>9.1540404040404</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.716082833365594</v>
+        <v>8.16252455376205</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
+      <c r="A13" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.916617386162044</v>
+        <v>1.6407852329329</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>9.1540404040404</v>
+        <v>3.12319259687681</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8.16252455376205</v>
+        <v>1.45877336702265</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
+      <c r="A14" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1.6407852329329</v>
+        <v>2.8826751225137</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3.12319259687681</v>
+        <v>-6.87044307347167</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.45877336702265</v>
+        <v>-9.47994085372972</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>16</v>
+      <c r="A15" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.8826751225137</v>
+        <v>0.336228635472136</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-6.87044307347167</v>
+        <v>11.4122252333634</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-9.47994085372972</v>
+        <v>11.0391075861624</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>17</v>
+      <c r="A16" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.336228635472136</v>
+        <v>1.81513543702876</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>11.4122252333634</v>
+        <v>6.24324324324326</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>11.0391075861624</v>
+        <v>4.349467204785</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>18</v>
+      <c r="A17" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.81513543702876</v>
+        <v>-2.71530444322545</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>6.24324324324326</v>
+        <v>-22.1826507250064</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4.349467204785</v>
+        <v>-20.0107589712198</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>19</v>
+      <c r="A18" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>-2.71530444322545</v>
+        <v>-0.620242458415554</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>-22.1826507250064</v>
+        <v>-0.490356325596597</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>-20.0107589712198</v>
+        <v>0.0672526147352803</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>20</v>
+      <c r="A19" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>-0.620242458415554</v>
+        <v>3.37588652482268</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.490356325596597</v>
+        <v>23.5545335085414</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.0672526147352803</v>
+        <v>19.595596755504</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>21</v>
+      <c r="A20" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3.37588652482268</v>
+        <v>1.45444566410538</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>23.5545335085414</v>
+        <v>5.71656474341931</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>19.595596755504</v>
+        <v>4.25245371132923</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>22</v>
+      <c r="A21" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1.45444566410538</v>
+        <v>1.92047606167163</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>5.71656474341931</v>
+        <v>1.68511066398391</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>4.25245371132923</v>
+        <v>-0.280669144981416</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>23</v>
+      <c r="A22" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>1.92047606167163</v>
+        <v>-0.238853503184699</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1.68511066398391</v>
+        <v>4.42740539203561</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>-0.280669144981416</v>
+        <v>4.67762679639883</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>24</v>
+      <c r="A23" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>-0.238853503184699</v>
+        <v>0.452247938281447</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>4.42740539203561</v>
+        <v>2.01326385599243</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4.67762679639883</v>
+        <v>1.55452870001871</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>25</v>
+      <c r="A24" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.452247938281447</v>
+        <v>-2.83368644067796</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>2.01326385599243</v>
+        <v>-8.89250058045042</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1.55452870001871</v>
+        <v>-6.23602745850979</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>26</v>
+      <c r="A25" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>-2.83368644067796</v>
+        <v>4.36086127010085</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-8.89250058045042</v>
+        <v>12.2579001019368</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-6.23602745850979</v>
+        <v>7.62038335670874</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>27</v>
+      <c r="A26" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>4.36086127010085</v>
+        <v>-1.04465917994254</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>12.2579001019368</v>
+        <v>-10.1475595913734</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>7.62038335670874</v>
+        <v>-9.24413553431799</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>28</v>
+      <c r="A27" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>-1.04465917994254</v>
+        <v>4.19635787806809</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>-10.1475595913734</v>
+        <v>23.1430015159171</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>-9.24413553431799</v>
+        <v>18.1839938732529</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>29</v>
+      <c r="A28" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>4.19635787806809</v>
+        <v>-2.45694022289766</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>23.1430015159171</v>
+        <v>-13.9926138695117</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>18.1839938732529</v>
+        <v>-11.8261714794865</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>30</v>
+      <c r="A29" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>-2.45694022289766</v>
+        <v>4.59620877694107</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-13.9926138695117</v>
+        <v>25.6440839694656</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>-11.8261714794865</v>
+        <v>20.1230995360801</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>31</v>
+      <c r="A30" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>4.59620877694107</v>
+        <v>0.496524329692138</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>25.6440839694656</v>
+        <v>2.08847541294854</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>20.1230995360801</v>
+        <v>1.58381768124809</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>32</v>
+      <c r="A31" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.496524329692138</v>
+        <v>-2.6185770750988</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>2.08847541294854</v>
+        <v>-21.2758043518691</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1.58381768124809</v>
+        <v>-19.1589312735732</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>33</v>
+      <c r="A32" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>-2.6185770750988</v>
+        <v>1.85185185185184</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-21.2758043518691</v>
+        <v>26.6950153555398</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-19.1589312735732</v>
+        <v>24.3914250060532</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>34</v>
+      <c r="A33" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1.85185185185184</v>
+        <v>1.39476961394771</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>26.6950153555398</v>
+        <v>-0.708558642550816</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>24.3914250060532</v>
+        <v>-2.07450551754084</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>35</v>
+      <c r="A34" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1.39476961394771</v>
+        <v>-6.01817735200197</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>-0.708558642550816</v>
+        <v>-11.5117370892019</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>-2.07450551754084</v>
+        <v>-5.88900866188085</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>36</v>
+      <c r="A35" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>-6.01817735200197</v>
+        <v>7.78881338212234</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>-11.5117370892019</v>
+        <v>27.5466893039049</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>-5.88900866188085</v>
+        <v>18.3850528025995</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
+      <c r="A36" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>7.78881338212234</v>
+        <v>-0.193986420950543</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>27.5466893039049</v>
+        <v>-2.92845257903493</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>18.3850528025995</v>
+        <v>-2.73927483325556</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
+      <c r="A37" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>-0.193986420950543</v>
+        <v>-0.0485908649173861</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>-2.92845257903493</v>
+        <v>9.41035310250255</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>-2.73927483325556</v>
+        <v>9.46310145336531</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
+      <c r="A38" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>-0.0485908649173861</v>
+        <v>0.0729217306757457</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>9.41035310250255</v>
+        <v>-5.12298292339025</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>9.46310145336531</v>
+        <v>-5.19229405812327</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
+      <c r="A39" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.0729217306757457</v>
+        <v>-5.73232936604323</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>-5.12298292339025</v>
+        <v>-6.10964332892999</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>-5.19229405812327</v>
+        <v>-0.3997362284751</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
+      <c r="A40" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>-5.73232936604323</v>
+        <v>7.5238340633857</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>-6.10964332892999</v>
+        <v>23.97115722828</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>-0.3997362284751</v>
+        <v>15.295988642336</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
+      <c r="A41" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>7.5238340633857</v>
+        <v>1.05439731607957</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>23.97115722828</v>
+        <v>4.36941410129097</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>15.295988642336</v>
+        <v>3.28086242518604</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
+      <c r="A42" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>1.05439731607957</v>
+        <v>1.23310410244248</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>4.36941410129097</v>
+        <v>0.978659779801561</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>3.28086242518604</v>
+        <v>-0.251632169940552</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>44</v>
+      <c r="A43" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>1.23310410244248</v>
+        <v>-0.093698758491445</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>0.978659779801561</v>
+        <v>0.524969713285772</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>-0.251632169940552</v>
+        <v>0.619461907115193</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
-        <v>45</v>
+      <c r="A44" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>-0.093698758491445</v>
+        <v>-2.03985932004689</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>0.524969713285772</v>
+        <v>-2.43706480985539</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.619461907115193</v>
+        <v>-0.405482581382066</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
-        <v>46</v>
+      <c r="A45" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>-2.03985932004689</v>
+        <v>1.81905217807563</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>-2.43706480985539</v>
+        <v>10.2113642602251</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>-0.405482581382066</v>
+        <v>8.24244509432881</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>47</v>
+      <c r="A46" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1.81905217807563</v>
+        <v>0.634696755994368</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>10.2113642602251</v>
+        <v>1.8804483188045</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>8.24244509432881</v>
+        <v>1.23752410417239</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
-        <v>48</v>
+      <c r="A47" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>0.634696755994368</v>
+        <v>0.0700770847932741</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1.8804483188045</v>
+        <v>-5.90392372570591</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1.23752410417239</v>
+        <v>-5.96964939822082</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
-        <v>49</v>
+      <c r="A48" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>0.0700770847932741</v>
+        <v>1.37721755368814</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>-5.90392372570591</v>
+        <v>6.18342426604313</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>-5.96964939822082</v>
+        <v>3.44812234267524</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>50</v>
+      <c r="A49" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>1.37721755368814</v>
+        <v>0.0460511167395872</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>6.18342426604313</v>
+        <v>0.966479080009797</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>3.44812234267524</v>
+        <v>2.21208469616112</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>51</v>
+      <c r="A50" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>0.0460511167395872</v>
+        <v>3.10701956271575</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>0.966479080009797</v>
+        <v>4.3014661335272</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>2.21208469616112</v>
+        <v>1.12789473684212</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
-        <v>52</v>
+      <c r="A51" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>3.10701956271575</v>
+        <v>0.803571428571437</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>4.3014661335272</v>
+        <v>4.182156133829</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>1.12789473684212</v>
+        <v>3.36051794757028</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>53</v>
+      <c r="A52" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>0.803571428571437</v>
+        <v>-0.99645704162975</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>4.182156133829</v>
+        <v>-5.24085637823373</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>3.36051794757028</v>
+        <v>-4.29556898288016</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
-        <v>54</v>
+      <c r="A53" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>-0.99645704162975</v>
+        <v>0.424960858868251</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>-5.24085637823373</v>
+        <v>9.83760884914098</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>-4.29556898288016</v>
+        <v>9.38132993807512</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
-        <v>55</v>
+      <c r="A54" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>0.424960858868251</v>
+        <v>-8.28507795100223</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>9.83760884914098</v>
+        <v>-23.0554960359974</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>9.38132993807512</v>
+        <v>-16.1135161135161</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>56</v>
+      <c r="A55" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>-8.28507795100223</v>
+        <v>3.4239922292375</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>-23.0554960359974</v>
+        <v>23.2664995822891</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>-16.1135161135161</v>
+        <v>19.1714449541284</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
-        <v>57</v>
+      <c r="A56" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>3.4239922292375</v>
+        <v>-1.59661892463021</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>23.2664995822891</v>
+        <v>-6.0996272450017</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>19.1714449541284</v>
+        <v>-4.53965886400269</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
-        <v>58</v>
+      <c r="A57" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>-1.59661892463021</v>
+        <v>4.17561441183489</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>-6.0996272450017</v>
+        <v>10.4174185011428</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>-4.53965886400269</v>
+        <v>5.9475806451613</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
-        <v>59</v>
+      <c r="A58" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>4.17561441183489</v>
+        <v>0.343563902885946</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>10.4174185011428</v>
+        <v>1.71042597232813</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>5.9475806451613</v>
+        <v>1.36726926736441</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
-        <v>60</v>
+      <c r="A59" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>0.343563902885946</v>
+        <v>0.228258388495761</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>1.71042597232813</v>
+        <v>3.56683804627249</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1.36726926736441</v>
+        <v>3.33733820175151</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
-        <v>61</v>
+      <c r="A60" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="B60" s="6" t="n">
-        <v>0.228258388495761</v>
+        <v>3.71213846504215</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>3.56683804627249</v>
+        <v>2.57524045919952</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>3.33733820175151</v>
+        <v>-1.08136339895997</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
-        <v>62</v>
+      <c r="A61" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="B61" s="6" t="n">
-        <v>3.71213846504215</v>
+        <v>-7.94905577514272</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>2.57524045919952</v>
+        <v>-10.1734220608994</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>-1.08136339895997</v>
+        <v>-2.41731097684157</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>63</v>
+      <c r="A62" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="B62" s="6" t="n">
-        <v>-7.94905577514272</v>
+        <v>2.24236641221374</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>-10.1734220608994</v>
+        <v>7.73375238522842</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>-2.41731097684157</v>
+        <v>5.35760495720787</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>64</v>
+      <c r="A63" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="B63" s="6" t="n">
-        <v>2.24236641221374</v>
+        <v>2.68315445636957</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>7.73375238522842</v>
+        <v>9.71035632423421</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>5.35760495720787</v>
+        <v>6.8585157596706</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
-        <v>65</v>
+      <c r="A64" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="B64" s="6" t="n">
-        <v>2.68315445636957</v>
+        <v>-2.86298568507157</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>9.71035632423421</v>
+        <v>-0.0664767331433946</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>6.8585157596706</v>
+        <v>2.8627070761104</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
-        <v>66</v>
+      <c r="A65" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="B65" s="6" t="n">
-        <v>-2.86298568507157</v>
+        <v>3.25146198830411</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>-0.0664767331433946</v>
+        <v>1.3494250688967</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2.8627070761104</v>
+        <v>-1.8298975354888</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
-        <v>67</v>
+      <c r="A66" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="B66" s="6" t="n">
-        <v>3.25146198830411</v>
+        <v>-0.0679655641141808</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>1.3494250688967</v>
+        <v>-1.09704641350211</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>-1.8298975354888</v>
+        <v>-1.0342258825477</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
-        <v>68</v>
+      <c r="A67" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="B67" s="6" t="n">
-        <v>-0.0679655641141808</v>
+        <v>-1.38290637043754</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>-1.09704641350211</v>
+        <v>-1.01441031475162</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>-1.0342258825477</v>
+        <v>0.373017300140921</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
-        <v>69</v>
+      <c r="A68" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="B68" s="6" t="n">
-        <v>-1.38290637043754</v>
+        <v>1.1264367816092</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>-1.01441031475162</v>
+        <v>5.0665645053156</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>0.373017300140921</v>
+        <v>3.88671085687622</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
-        <v>70</v>
+      <c r="A69" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="B69" s="6" t="n">
-        <v>1.1264367816092</v>
+        <v>-0.500113662195956</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>5.0665645053156</v>
+        <v>2.7894257064722</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>3.88671085687622</v>
+        <v>3.30376335461517</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
-        <v>71</v>
+      <c r="A70" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="B70" s="6" t="n">
-        <v>-0.500113662195956</v>
+        <v>0.891021247429724</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>2.7894257064722</v>
+        <v>3.29904221355091</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>3.30376335461517</v>
+        <v>2.40459645172562</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
-        <v>72</v>
+      <c r="A71" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="B71" s="6" t="n">
-        <v>0.891021247429724</v>
+        <v>-1.1322463768116</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>3.29904221355091</v>
+        <v>2.0518543956044</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>2.40459645172562</v>
+        <v>3.20906499256965</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B72" s="6" t="n">
-        <v>-1.1322463768116</v>
-      </c>
+      <c r="A72" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="6"/>
       <c r="C72" s="6" t="n">
-        <v>2.0518543956044</v>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>3.20906499256965</v>
-      </c>
+        <v>4.62690333978295</v>
+      </c>
+      <c r="D72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5" t="s">
-        <v>74</v>
+      <c r="A73" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="n">
-        <v>4.62690333978295</v>
+        <v>4.25343732411352</v>
       </c>
       <c r="D73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5" t="s">
-        <v>75</v>
+      <c r="A74" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="n">
-        <v>4.25343732411352</v>
+        <v>-4.07990128027147</v>
       </c>
       <c r="D74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5" t="s">
-        <v>74</v>
+      <c r="A75" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="6" t="n">
-        <v>-4.07990128027147</v>
+        <v>4.25343732411352</v>
       </c>
       <c r="D75" s="6"/>
     </row>
-    <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6" t="n">
-        <v>4.25343732411352</v>
-      </c>
-      <c r="D76" s="6"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="s">
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
-      <c r="N77" s="7"/>
-      <c r="O77" s="7"/>
-      <c r="P77" s="7"/>
-      <c r="Q77" s="7"/>
-      <c r="R77" s="7"/>
-      <c r="S77" s="8"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9"/>
+      <c r="O77" s="9"/>
+      <c r="P77" s="9"/>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
+      <c r="S77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9"/>
-      <c r="K78" s="9"/>
-      <c r="L78" s="9"/>
-      <c r="M78" s="9"/>
-      <c r="N78" s="9"/>
-      <c r="O78" s="9"/>
-      <c r="P78" s="9"/>
-      <c r="Q78" s="9"/>
-      <c r="R78" s="9"/>
-      <c r="S78" s="9"/>
+      <c r="A78" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
+      <c r="M78" s="12"/>
+      <c r="N78" s="12"/>
+      <c r="O78" s="12"/>
+      <c r="P78" s="12"/>
+      <c r="Q78" s="12"/>
+      <c r="R78" s="12"/>
+      <c r="S78" s="12"/>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A77:R77"/>
-    <mergeCell ref="A78:S78"/>
+  <mergeCells count="3">
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A78:D78"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
